--- a/stories/arbres/ATOM-REL.MOQ.001-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugues est à l'école. La classe range les manteaux. Lila fait tomber son bonnet. Nino commence à rire. Le rire est court. Hugues ne rit pas. Il ne faut pas rire. Hugues ne répète pas. Il ne faut pas répéter. Hugues dit : ce n'est pas gentil. Il ramasse le bonnet. Il le tend. Lila le remet. La maîtresse s'approche. Nino dit : pardon. Plus tard, à la maison, un dessin glisse. Encore un petit rire. Hugues se souvient. Il ne rit pas. Il ne répète pas. Il dit : ce n'est pas gentil. Maman entend. Maman dit : tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. On dit : ce n'est pas gentil. Hugues serre la main de maman.</t>
+          <t>Hugues est à l'école. La classe range les manteaux. Lila fait tomber son bonnet. Nino commence à rire. Le rire est court. Hugues ne rit pas. Il ne faut pas rire. Hugues ne répète pas. Il ne faut pas répéter. Ce n'est pas gentil. Il ramasse le bonnet. Il le tend. Lila le remet. La maîtresse s'approche. Pardon. Plus tard, à la maison, un dessin glisse. Encore un petit rire. Hugues se souvient. Il ne rit pas. Il ne répète pas. Ce n'est pas gentil. Maman entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Hugues serre la main de maman.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hugues est à l'école. La classe range les manteaux. Lila fait tomber son bonnet. Nino commence à rire. Le rire est court. Hugues ne rit pas. Il ne faut pas rire. Hugues ne répète pas. Il ne faut pas répéter.
+enfant-m|Ce n'est pas gentil. Il ramasse le bonnet. Il le tend.
+narrateur|Lila le remet. La maîtresse s'approche.
+copain|Pardon. Plus tard, à la maison, un dessin glisse. Encore un petit rire.
+narrateur|Hugues se souvient. Il ne rit pas. Il ne répète pas.
+narrateur|Ce n'est pas gentil. Maman entend.
+maman|Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter.
+narrateur|Ce n'est pas gentil.
+narrateur|Hugues serre la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1467,6 +1496,11 @@
           <t>question d'écoute, ne change pas le cours</t>
         </is>
       </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Nino rit. Que fait Hugues ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1491,7 +1525,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugues n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. Maman est là.</t>
+          <t>Hugues n'a pas ri. Il n'a pas répété. Il Ce n'est pas gentil. Maman est là.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1633,6 +1667,12 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hugues n'a pas ri. Il n'a pas répété. Il
+enfant-f|Ce n'est pas gentil. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1831,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hugues range son cartable. Maman marche à côté.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1998,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2021,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2038,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Hugues serre la main de maman.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1501,6 +1507,7 @@
           <t>narrateur|Nino rit. Que fait Hugues ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1673,6 +1680,7 @@
 enfant-f|Ce n'est pas gentil. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1836,6 +1844,7 @@
           <t>narrateur|Hugues range son cartable. Maman marche à côté.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2003,6 +2012,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2021,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2045,6 +2055,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2059,7 +2083,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2246,6 +2270,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.MOQ.001-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hugues ne rit pas, deux fois</t>
+          <t>Le bonnet et le dessin</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Un bonnet glisse à l'école, puis un dessin à la maison. Victorino n'est pas là pour rire. Il aide, deux fois.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hugues est à l'école. La classe range les manteaux. Lila fait tomber son bonnet. Nino commence à rire. Le rire est court. Hugues ne rit pas. Il ne faut pas rire. Hugues ne répète pas. Il ne faut pas répéter. Ce n'est pas gentil. Il ramasse le bonnet. Il le tend. Lila le remet. La maîtresse s'approche. Pardon. Plus tard, à la maison, un dessin glisse. Encore un petit rire. Hugues se souvient. Il ne rit pas. Il ne répète pas. Ce n'est pas gentil. Maman entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Hugues serre la main de maman.</t>
+          <t>Les bonnets de laine sont alignés sur la tablette. Ça sent le mouton doux. La porte vitrée laisse entrer un carré de lumière. Un fil de laine brille, tout fin. Ton bonnet gris est bien à sa place, Victorino. Tu as vu le carré de soleil ? Oui, maman. Il est chaud. Je reviens te chercher. On dessinera à la maison. D'accord. En ce moment, la classe range les manteaux. Mila tient un bonnet jaune. Le bonnet glisse. Il tombe près de la tablette. Un camarade commence un petit rire. Le rire est court. Victorino n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le bonnet. La laine est douce sous les doigts. Il le tend. Merci, Victorino. Mila remet le bonnet. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, à la maison, la table sent le crayon. Une chaise frotte un peu le carrelage. Un verre d'eau fait un rond clair. On dessine ici, Victorino. Le papier est à plat. Oui, maman. Un dessin de Mila glisse. Il tombe près de la chaise. Encore un petit rire, tout court. Victorino se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le dessin. Il le tend. Merci. Maman entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. C'est du bon travail. Tu as du crayon sur le pouce ? Un peu. On essuie. Victorino serre la main de maman. Le carré de lumière a bougé sur le plancher. Le dessin est à plat, sur la table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,15 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hugues est à l'école. La classe range les manteaux. Lila fait tomber son bonnet. Nino commence à rire. Le rire est court. Hugues ne rit pas. Il ne faut pas rire. Hugues ne répète pas. Il ne faut pas répéter.
-enfant-m|Ce n'est pas gentil. Il ramasse le bonnet. Il le tend.
-narrateur|Lila le remet. La maîtresse s'approche.
-copain|Pardon. Plus tard, à la maison, un dessin glisse. Encore un petit rire.
-narrateur|Hugues se souvient. Il ne rit pas. Il ne répète pas.
-narrateur|Ce n'est pas gentil. Maman entend.
-maman|Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter.
-narrateur|Ce n'est pas gentil.
-narrateur|Hugues serre la main de maman.</t>
+          <t>narrateur|Les bonnets de laine sont alignés sur la tablette.
+narrateur|Ça sent le mouton doux.
+narrateur|La porte vitrée laisse entrer un carré de lumière.
+narrateur|Un fil de laine brille, tout fin.
+maman|Ton bonnet gris est bien à sa place, Victorino.
+maman|Tu as vu le carré de soleil ?
+enfant-m|Oui, maman.
+enfant-m|Il est chaud.
+maman|Je reviens te chercher.
+maman|On dessinera à la maison.
+enfant-m|D'accord.
+narrateur|En ce moment, la classe range les manteaux.
+narrateur|Mila tient un bonnet jaune.
+narrateur|Le bonnet glisse.
+narrateur|Il tombe près de la tablette.
+narrateur|Un camarade commence un petit rire.
+narrateur|Le rire est court.
+narrateur|Victorino n'est pas là pour rire.
+narrateur|Il ne répète pas.
+enfant-m|Ce n'est pas gentil.
+narrateur|Il ramasse le bonnet.
+narrateur|La laine est douce sous les doigts.
+narrateur|Il le tend.
+copine|Merci, Victorino.
+narrateur|Mila remet le bonnet.
+narrateur|La maîtresse s'approche.
+maitresse|On aide.
+maitresse|On n'est pas là pour rire.
+maitresse|On n'est pas là pour répéter.
+enfant-m|On aide.
+narrateur|Plus tard, à la maison, la table sent le crayon.
+narrateur|Une chaise frotte un peu le carrelage.
+narrateur|Un verre d'eau fait un rond clair.
+maman|On dessine ici, Victorino.
+maman|Le papier est à plat.
+enfant-m|Oui, maman.
+narrateur|Un dessin de Mila glisse.
+narrateur|Il tombe près de la chaise.
+narrateur|Encore un petit rire, tout court.
+narrateur|Victorino se souvient.
+narrateur|Il n'est pas là pour rire.
+narrateur|Il ne répète pas.
+enfant-m|Ce n'est pas gentil.
+narrateur|Il ramasse le dessin.
+narrateur|Il le tend.
+copine|Merci.
+narrateur|Maman entend.
+maman|Tu as bien fait.
+maman|Même leçon, autre lieu.
+maman|Il ne faut pas rire.
+maman|Il ne faut pas répéter.
+maman|Ce n'est pas gentil.
+maman|C'est du bon travail.
+maman|Tu as du crayon sur le pouce ?
+enfant-m|Un peu.
+maman|On essuie.
+narrateur|Victorino serre la main de maman.
+narrateur|Le carré de lumière a bougé sur le plancher.
+narrateur|Le dessin est à plat, sur la table.</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr"/>
@@ -1348,7 +1410,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Nino rit. Que fait Hugues ?</t>
+          <t>Un camarade rit. Que fait Victorino ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1504,7 +1566,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Nino rit. Que fait Hugues ?</t>
+          <t>narrateur|Un camarade rit.
+narrateur|Que fait Victorino ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1532,7 +1595,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hugues n'a pas ri. Il n'a pas répété. Il Ce n'est pas gentil. Maman est là.</t>
+          <t>Victorino n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis à la maison. Tu as ramassé le bonnet. Puis le dessin. Bravo. C'est du bon travail. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1676,8 +1739,18 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hugues n'a pas ri. Il n'a pas répété. Il
-enfant-f|Ce n'est pas gentil. Maman est là.</t>
+          <t>narrateur|Victorino n'a pas ri.
+narrateur|Il n'a pas répété.
+narrateur|Il a dit : ce n'est pas gentil.
+narrateur|À l'école, puis à la maison.
+maman|Tu as ramassé le bonnet.
+maman|Puis le dessin.
+maman|Bravo.
+maman|C'est du bon travail.
+enfant-m|On aide.
+enfant-m|Deux fois.
+maman|Oui.
+maman|Même geste, autre lieu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1705,7 +1778,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hugues range son cartable. Maman marche à côté.</t>
+          <t>Victorino range son cartable près de la porte. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, maman. Le dessin de Mila est à plat. On reste un peu à table ? Oui. Maman marche à côté. La laine des bonnets sent encore le mouton, loin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1841,7 +1914,15 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hugues range son cartable. Maman marche à côté.</t>
+          <t>narrateur|Victorino range son cartable près de la porte.
+narrateur|Le zip fait un petit bruit.
+maman|Tu as fini de ranger ?
+enfant-m|Oui, maman.
+maman|Le dessin de Mila est à plat.
+maman|On reste un peu à table ?
+enfant-m|Oui.
+narrateur|Maman marche à côté.
+narrateur|La laine des bonnets sent encore le mouton, loin.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1869,7 +1950,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai ramassé. À l'école, puis à la maison. Bravo. Tu as fait du bon travail. Le carré de lumière a glissé jusqu'à la table. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2009,7 +2090,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai ramassé.
+enfant-m|À l'école, puis à la maison.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|Le carré de lumière a glissé jusqu'à la table.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2031,7 +2117,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2069,6 +2155,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les bonnets de laine sont alignés sur la tablette. Ça sent le mouton doux. La porte vitrée laisse entrer un carré de lumière. Un fil de laine brille, tout fin. Ton bonnet gris est bien à sa place, Victorino. Tu as vu le carré de soleil ? Oui, maman. Il est chaud. Je reviens te chercher. On dessinera à la maison. D'accord. En ce moment, la classe range les manteaux. Mila tient un bonnet jaune. Le bonnet glisse. Il tombe près de la tablette. Un camarade commence un petit rire. Le rire est court. Victorino n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le bonnet. La laine est douce sous les doigts. Il le tend. Merci, Victorino. Mila remet le bonnet. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, à la maison, la table sent le crayon. Une chaise frotte un peu le carrelage. Un verre d'eau fait un rond clair. On dessine ici, Victorino. Le papier est à plat. Oui, maman. Un dessin de Mila glisse. Il tombe près de la chaise. Encore un petit rire, tout court. Victorino se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le dessin. Il le tend. Merci. Maman entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. C'est du bon travail. Tu as du crayon sur le pouce ? Un peu. On essuie. Victorino serre la main de maman. Le carré de lumière a bougé sur le plancher. Le dessin est à plat, sur la table.</t>
+          <t>Les bonnets de laine sont alignés sur la tablette. Ça sent le mouton doux. La porte vitrée laisse entrer un carré de lumière. Un fil de laine brille, tout fin. Ton bonnet gris est bien à sa place, Victorino. Tu as vu le carré de soleil ? Oui, maman. Il est chaud. Je reviens te chercher. On dessinera à la maison. D'accord. En ce moment, la classe range les manteaux. Mila tient un bonnet jaune. Le bonnet glisse. Il tombe près de la tablette. Un camarade commence un petit rire. Le rire est court. Victorino n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le bonnet. La laine est douce sous les doigts. Il le tend. Merci, Victorino. Mila remet le bonnet. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, à la maison, la table sent le crayon. Une chaise frotte un peu le carrelage. Un verre d'eau fait un rond clair. On dessine ici, Victorino. Le papier est à plat. Oui, maman. Un dessin de Mila glisse. Il tombe près de la chaise. Encore un petit rire, tout court. Victorino se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le dessin. Il le tend. Merci. Maman entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Tu as du crayon sur le pouce ? Un peu. On essuie. Victorino serre la main de maman. Le carré de lumière a bougé sur le plancher. Le dessin est à plat, sur la table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugues est à l'école. La classe range les manteaux. Lila fait tomber son bonnet. Nino commence à rire. Le rire est court. Hugues ne rit &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt;. Il ne faut pas rire. Hugues ne répète pas. Il ne faut pas répéter. Hugues dit : ce n'est pas gentil. Il ramasse le bonnet. Il le tend. Lila le remet. La maîtresse s'approche. Nino dit : pardon. Plus tard, à la maison, un dessin glisse. Encore un petit rire. Hugues se souvient. Il ne rit pas. Il ne répète pas. Il dit : ce n'est pas gentil. Maman entend. Maman dit : tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. On dit : ce n'est pas gentil. Hugues serre la main de maman.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Les bonnets de laine sont alignés sur la tablette. Ça sent le mouton doux. La porte vitrée laisse entrer un carré de lumière. Un fil de laine brille, tout fin. Ton bonnet gris est bien à sa place, Victorino. Tu as vu le carré de soleil ? Oui, maman. Il est chaud. Je reviens te chercher. On dessinera à la maison. D'accord. En ce moment, la classe range les manteaux. Mila tient un bonnet jaune. Le bonnet glisse. Il tombe près de la tablette. Un camarade commence un petit rire. Le rire est court. Victorino n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le bonnet. La laine est douce sous les doigts. Il le tend. Merci, Victorino. Mila remet le bonnet. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, à la maison, la table sent le crayon. Une chaise frotte un peu le carrelage. Un verre d'eau fait un rond clair. On dessine ici, Victorino. Le papier est à plat. Oui, maman. Un dessin de Mila glisse. Il tombe près de la chaise. Encore un petit rire, tout court. Victorino se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le dessin. Il le tend. Merci. Maman entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Tu as du crayon sur le pouce ? Un peu. On essuie. Victorino serre la main de maman. Le carré de lumière a bougé sur le plancher. Le dessin est à plat, sur la table.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1376,7 +1376,6 @@
 maman|Il ne faut pas rire.
 maman|Il ne faut pas répéter.
 maman|Ce n'est pas gentil.
-maman|C'est du bon travail.
 maman|Tu as du crayon sur le pouce ?
 enfant-m|Un peu.
 maman|On essuie.
@@ -1385,7 +1384,6 @@
 narrateur|Le dessin est à plat, sur la table.</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1415,7 +1413,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Nino rit. Que fait Hugues ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Un camarade rit. Que fait Victorino ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1570,7 +1568,6 @@
 narrateur|Que fait Victorino ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1595,12 +1592,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis à la maison. Tu as ramassé le bonnet. Puis le dessin. Bravo. C'est du bon travail. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
+          <t>Victorino n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis à la maison. Tu as ramassé le bonnet. Puis le dessin. Bravo. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugues n'a &lt;emphasis level="moderate"&gt;pas&lt;/emphasis&gt; ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis à la maison. Tu as ramassé le bonnet. Puis le dessin. Bravo. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1746,14 +1743,12 @@
 maman|Tu as ramassé le bonnet.
 maman|Puis le dessin.
 maman|Bravo.
-maman|C'est du bon travail.
 enfant-m|On aide.
 enfant-m|Deux fois.
 maman|Oui.
 maman|Même geste, autre lieu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1783,7 +1778,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hugues range son cartable. Maman marche à côté.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Victorino range son cartable près de la porte. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, maman. Le dessin de Mila est à plat. On reste un peu à table ? Oui. Maman marche à côté. La laine des bonnets sent encore le mouton, loin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1925,7 +1920,6 @@
 narrateur|La laine des bonnets sent encore le mouton, loin.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1950,12 +1944,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai ramassé. À l'école, puis à la maison. Bravo. Tu as fait du bon travail. Le carré de lumière a glissé jusqu'à la table. L'histoire est finie.</t>
+          <t>J'ai ramassé. À l'école, puis à la maison. Bravo. Le carré de lumière a glissé jusqu'à la table.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai ramassé. À l'école, puis à la maison. Bravo. Le carré de lumière a glissé jusqu'à la table.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2093,12 +2087,9 @@
           <t>enfant-m|J'ai ramassé.
 enfant-m|À l'école, puis à la maison.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|Le carré de lumière a glissé jusqu'à la table.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|Le carré de lumière a glissé jusqu'à la table.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2117,7 +2108,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2162,6 +2153,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-06.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hugues, Lila, Nino, maman</t>
+          <t>Victorino, Mila, maman</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.MOQ.001-06.xlsx
+++ b/stories/arbres/ATOM-REL.MOQ.001-06.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Le bonnet et le dessin</t>
+          <t>Le bonnet sur la tablette</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>école puis maison</t>
+          <t>école, tablette de laine, puis table à la maison</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Un bonnet glisse à l'école, puis un dessin à la maison. Victorino n'est pas là pour rire. Il aide, deux fois.</t>
+          <t>Victorino veut dessiner une maison avec Mila. Le bonnet jaune tombe. Un rire commence. Mila a le visage triste. Il s'arrête, tend le bonnet. À la maison, le dessin glisse. Même geste vécu. Ils dessinent ensemble.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Les bonnets de laine sont alignés sur la tablette. Ça sent le mouton doux. La porte vitrée laisse entrer un carré de lumière. Un fil de laine brille, tout fin. Ton bonnet gris est bien à sa place, Victorino. Tu as vu le carré de soleil ? Oui, maman. Il est chaud. Je reviens te chercher. On dessinera à la maison. D'accord. En ce moment, la classe range les manteaux. Mila tient un bonnet jaune. Le bonnet glisse. Il tombe près de la tablette. Un camarade commence un petit rire. Le rire est court. Victorino n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le bonnet. La laine est douce sous les doigts. Il le tend. Merci, Victorino. Mila remet le bonnet. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, à la maison, la table sent le crayon. Une chaise frotte un peu le carrelage. Un verre d'eau fait un rond clair. On dessine ici, Victorino. Le papier est à plat. Oui, maman. Un dessin de Mila glisse. Il tombe près de la chaise. Encore un petit rire, tout court. Victorino se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le dessin. Il le tend. Merci. Maman entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Tu as du crayon sur le pouce ? Un peu. On essuie. Victorino serre la main de maman. Le carré de lumière a bougé sur le plancher. Le dessin est à plat, sur la table.</t>
+          <t>Un fil de laine brille sur la tablette. Les bonnets sentent le mouton doux. La porte vitrée laisse un carré de lumière. Le carré est chaud sur le bois. Ton bonnet gris est à sa place, Victorino. Tu as vu le carré de soleil ? Oui, maman. Il est chaud. Je reviens te chercher. On dessinera à la maison. D'accord. Maman part vers la porte vitrée. En ce moment, Mila tient un bonnet jaune. La laine est douce, un peu lourde. On le met sur la tablette ? Oui. Le bonnet glisse. Il tombe près de la tablette. Un petit rire commence dans la gorge de Victorino. Mila baisse les yeux. Sa lèvre tremble un peu. Le bonnet reste par terre. Victorino referme la bouche. Le rire ne sort plus. Il ramasse le bonnet. La laine est douce sous les doigts. Il le tend. Merci, Victorino. Mila remet le bonnet. Il est bien là. Oui. La maîtresse s'approche. Votre bonnet est à sa place ? Oui. Vous pouvez aller dessiner, alors. Plus tard, à la maison, la table sent le crayon. Une chaise frotte un peu le carrelage. Un verre d'eau fait un rond clair. On dessine ici, Victorino. Le papier est à plat. Une maison, Mila ? Oui. Un dessin de Mila glisse. Il tombe près de la chaise. Un petit rire recommence, tout court. Mila regarde le papier. Ses joues baissent. Victorino referme encore la bouche. Il ramasse le dessin. Le papier est un peu froid. Il le tend. Merci. On dessine la porte ? Oui, et une fenêtre. Le crayon pose un toit, tout doux. Vous dessinez ensemble ? Oui, maman. Bravo, Victorino. Tu as du crayon sur le pouce ? Un peu. On essuie ? Oui. Victorino serre la main de maman. Le carré de lumière a bougé sur le plancher. Le dessin est à plat, sur la table.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Les bonnets de laine sont alignés sur la tablette. Ça sent le mouton doux. La porte vitrée laisse entrer un carré de lumière. Un fil de laine brille, tout fin. Ton bonnet gris est bien à sa place, Victorino. Tu as vu le carré de soleil ? Oui, maman. Il est chaud. Je reviens te chercher. On dessinera à la maison. D'accord. En ce moment, la classe range les manteaux. Mila tient un bonnet jaune. Le bonnet glisse. Il tombe près de la tablette. Un camarade commence un petit rire. Le rire est court. Victorino n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le bonnet. La laine est douce sous les doigts. Il le tend. Merci, Victorino. Mila remet le bonnet. La maîtresse s'approche. On aide. On n'est pas là pour rire. On n'est pas là pour répéter. On aide. Plus tard, à la maison, la table sent le crayon. Une chaise frotte un peu le carrelage. Un verre d'eau fait un rond clair. On dessine ici, Victorino. Le papier est à plat. Oui, maman. Un dessin de Mila glisse. Il tombe près de la chaise. Encore un petit rire, tout court. Victorino se souvient. Il n'est pas là pour rire. Il ne répète pas. Ce n'est pas gentil. Il ramasse le dessin. Il le tend. Merci. Maman entend. Tu as bien fait. Même leçon, autre lieu. Il ne faut pas rire. Il ne faut pas répéter. Ce n'est pas gentil. Tu as du crayon sur le pouce ? Un peu. On essuie. Victorino serre la main de maman. Le carré de lumière a bougé sur le plancher. Le dessin est à plat, sur la table.</t>
+          <t>Un fil de laine brille sur la tablette. Les bonnets sentent le mouton doux. La porte vitrée laisse un carré de lumière. Le carré est chaud sur le bois. Ton bonnet gris est à sa place, Victorino. Tu as vu le carré de soleil ? Oui, maman. Il est chaud. Je reviens te chercher. On dessinera à la maison. D'accord. Maman part vers la porte vitrée. En ce moment, Mila tient un bonnet jaune. La laine est douce, un peu lourde. On le met sur la tablette ? Oui. Le bonnet glisse. Il tombe près de la tablette. Un petit rire commence dans la gorge de Victorino. Mila baisse les yeux. Sa lèvre tremble un peu. Le bonnet reste par terre. Victorino referme la bouche. Le rire ne sort plus. Il ramasse le bonnet. La laine est douce sous les doigts. Il le tend. Merci, Victorino. Mila remet le bonnet. Il est bien là. Oui. La maîtresse s'approche. Votre bonnet est à sa place ? Oui. Vous pouvez aller dessiner, alors. Plus tard, à la maison, la table sent le crayon. Une chaise frotte un peu le carrelage. Un verre d'eau fait un rond clair. On dessine ici, Victorino. Le papier est à plat. Une maison, Mila ? Oui. Un dessin de Mila glisse. Il tombe près de la chaise. Un petit rire recommence, tout court. Mila regarde le papier. Ses joues baissent. Victorino referme encore la bouche. Il ramasse le dessin. Le papier est un peu froid. Il le tend. Merci. On dessine la porte ? Oui, et une fenêtre. Le crayon pose un toit, tout doux. Vous dessinez ensemble ? Oui, maman. Bravo, Victorino. Tu as du crayon sur le pouce ? Un peu. On essuie ? Oui. Victorino serre la main de maman. Le carré de lumière a bougé sur le plancher. Le dessin est à plat, sur la table.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1252,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1324,61 +1324,68 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Les bonnets de laine sont alignés sur la tablette.
-narrateur|Ça sent le mouton doux.
-narrateur|La porte vitrée laisse entrer un carré de lumière.
-narrateur|Un fil de laine brille, tout fin.
-maman|Ton bonnet gris est bien à sa place, Victorino.
+          <t>narrateur|Un fil de laine brille sur la tablette.
+narrateur|Les bonnets sentent le mouton doux.
+narrateur|La porte vitrée laisse un carré de lumière.
+narrateur|Le carré est chaud sur le bois.
+maman|Ton bonnet gris est à sa place, Victorino.
 maman|Tu as vu le carré de soleil ?
 enfant-m|Oui, maman.
 enfant-m|Il est chaud.
 maman|Je reviens te chercher.
 maman|On dessinera à la maison.
 enfant-m|D'accord.
-narrateur|En ce moment, la classe range les manteaux.
-narrateur|Mila tient un bonnet jaune.
+narrateur|Maman part vers la porte vitrée.
+narrateur|En ce moment, Mila tient un bonnet jaune.
+narrateur|La laine est douce, un peu lourde.
+enfant-m|On le met sur la tablette ?
+copine|Oui.
 narrateur|Le bonnet glisse.
 narrateur|Il tombe près de la tablette.
-narrateur|Un camarade commence un petit rire.
-narrateur|Le rire est court.
-narrateur|Victorino n'est pas là pour rire.
-narrateur|Il ne répète pas.
-enfant-m|Ce n'est pas gentil.
+narrateur|Un petit rire commence dans la gorge de Victorino.
+narrateur|Mila baisse les yeux.
+narrateur|Sa lèvre tremble un peu.
+narrateur|Le bonnet reste par terre.
+narrateur|Victorino referme la bouche.
+narrateur|Le rire ne sort plus.
 narrateur|Il ramasse le bonnet.
 narrateur|La laine est douce sous les doigts.
 narrateur|Il le tend.
 copine|Merci, Victorino.
 narrateur|Mila remet le bonnet.
+enfant-m|Il est bien là.
+copine|Oui.
 narrateur|La maîtresse s'approche.
-maitresse|On aide.
-maitresse|On n'est pas là pour rire.
-maitresse|On n'est pas là pour répéter.
-enfant-m|On aide.
+maitresse|Votre bonnet est à sa place ?
+copine|Oui.
+maitresse|Vous pouvez aller dessiner, alors.
 narrateur|Plus tard, à la maison, la table sent le crayon.
 narrateur|Une chaise frotte un peu le carrelage.
 narrateur|Un verre d'eau fait un rond clair.
 maman|On dessine ici, Victorino.
 maman|Le papier est à plat.
-enfant-m|Oui, maman.
+enfant-m|Une maison, Mila ?
+copine|Oui.
 narrateur|Un dessin de Mila glisse.
 narrateur|Il tombe près de la chaise.
-narrateur|Encore un petit rire, tout court.
-narrateur|Victorino se souvient.
-narrateur|Il n'est pas là pour rire.
-narrateur|Il ne répète pas.
-enfant-m|Ce n'est pas gentil.
+narrateur|Un petit rire recommence, tout court.
+narrateur|Mila regarde le papier.
+narrateur|Ses joues baissent.
+narrateur|Victorino referme encore la bouche.
 narrateur|Il ramasse le dessin.
+narrateur|Le papier est un peu froid.
 narrateur|Il le tend.
 copine|Merci.
-narrateur|Maman entend.
-maman|Tu as bien fait.
-maman|Même leçon, autre lieu.
-maman|Il ne faut pas rire.
-maman|Il ne faut pas répéter.
-maman|Ce n'est pas gentil.
+enfant-m|On dessine la porte ?
+copine|Oui, et une fenêtre.
+narrateur|Le crayon pose un toit, tout doux.
+maman|Vous dessinez ensemble ?
+enfant-m|Oui, maman.
+maman|Bravo, Victorino.
 maman|Tu as du crayon sur le pouce ?
 enfant-m|Un peu.
-maman|On essuie.
+maman|On essuie ?
+enfant-m|Oui.
 narrateur|Victorino serre la main de maman.
 narrateur|Le carré de lumière a bougé sur le plancher.
 narrateur|Le dessin est à plat, sur la table.</t>
@@ -1428,7 +1435,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>pas rire | pas gentil | ne pas rire | pas répéter</t>
+          <t>pas rire | pas gentil | ne pas rire | pas répéter | ramasse | il ramasse | il tend</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1443,7 +1450,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il ne rit pas. Il dit que ce n'est pas gentil. Que fait Hugues ?</t>
+          <t>Victorino voit le visage de Mila. Que fait-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1485,14 +1492,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1592,12 +1599,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Victorino n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis à la maison. Tu as ramassé le bonnet. Puis le dessin. Bravo. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
+          <t>Victorino a vu le visage de Mila. Le rire s'est arrêté. Il a tendu le bonnet, puis le dessin. Bravo. Vous avez une maison, maintenant. Avec une fenêtre. Oui.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Victorino n'a pas ri. Il n'a pas répété. Il a dit : ce n'est pas gentil. À l'école, puis à la maison. Tu as ramassé le bonnet. Puis le dessin. Bravo. On aide. Deux fois. Oui. Même geste, autre lieu.</t>
+          <t>Victorino a vu le visage de Mila. Le rire s'est arrêté. Il a tendu le bonnet, puis le dessin. Bravo. Vous avez une maison, maintenant. Avec une fenêtre. Oui.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1660,7 +1667,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1736,17 +1743,13 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Victorino n'a pas ri.
-narrateur|Il n'a pas répété.
-narrateur|Il a dit : ce n'est pas gentil.
-narrateur|À l'école, puis à la maison.
-maman|Tu as ramassé le bonnet.
-maman|Puis le dessin.
+          <t>narrateur|Victorino a vu le visage de Mila.
+narrateur|Le rire s'est arrêté.
+narrateur|Il a tendu le bonnet, puis le dessin.
 maman|Bravo.
-enfant-m|On aide.
-enfant-m|Deux fois.
-maman|Oui.
-maman|Même geste, autre lieu.</t>
+maman|Vous avez une maison, maintenant.
+enfant-m|Avec une fenêtre.
+maman|Oui.</t>
         </is>
       </c>
     </row>
@@ -1773,12 +1776,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Victorino range son cartable près de la porte. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, maman. Le dessin de Mila est à plat. On reste un peu à table ? Oui. Maman marche à côté. La laine des bonnets sent encore le mouton, loin.</t>
+          <t>Victorino range son cartable près de la porte. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, maman. Le dessin de Mila est à plat. On reste un peu à table ? Oui. Maman marche à côté. Le toit est bien droit ? Oui, tout droit. La laine des bonnets sent encore le mouton, loin.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Victorino range son cartable près de la porte. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, maman. Le dessin de Mila est à plat. On reste un peu à table ? Oui. Maman marche à côté. La laine des bonnets sent encore le mouton, loin.</t>
+          <t>Victorino range son cartable près de la porte. Le zip fait un petit bruit. Tu as fini de ranger ? Oui, maman. Le dessin de Mila est à plat. On reste un peu à table ? Oui. Maman marche à côté. Le toit est bien droit ? Oui, tout droit. La laine des bonnets sent encore le mouton, loin.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1841,7 +1844,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1917,6 +1920,8 @@
 maman|On reste un peu à table ?
 enfant-m|Oui.
 narrateur|Maman marche à côté.
+maman|Le toit est bien droit ?
+enfant-m|Oui, tout droit.
 narrateur|La laine des bonnets sent encore le mouton, loin.</t>
         </is>
       </c>
@@ -1944,12 +1949,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai ramassé. À l'école, puis à la maison. Bravo. Le carré de lumière a glissé jusqu'à la table.</t>
+          <t>On a dessiné la maison. Avec Mila. Bravo. Le carré de lumière a glissé jusqu'à la table.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>J'ai ramassé. À l'école, puis à la maison. Bravo. Le carré de lumière a glissé jusqu'à la table.</t>
+          <t>On a dessiné la maison. Avec Mila. Bravo. Le carré de lumière a glissé jusqu'à la table.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2012,7 +2017,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2084,8 +2089,8 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|J'ai ramassé.
-enfant-m|À l'école, puis à la maison.
+          <t>enfant-m|On a dessiné la maison.
+enfant-m|Avec Mila.
 maman|Bravo.
 narrateur|Le carré de lumière a glissé jusqu'à la table.</t>
         </is>
@@ -2108,7 +2113,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2158,6 +2163,13 @@
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
